--- a/artfynd/A 23955-2025 artfynd.xlsx
+++ b/artfynd/A 23955-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -887,6 +887,229 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128331640</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Jangmossen, Jangmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>407245</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6652297</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128331813</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98473</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Jangmossen, Jangmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>407208</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6652345</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23955-2025 artfynd.xlsx
+++ b/artfynd/A 23955-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>128331640</v>
       </c>
       <c r="B4" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128331813</v>
       </c>
       <c r="B5" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23955-2025 artfynd.xlsx
+++ b/artfynd/A 23955-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>128331640</v>
       </c>
       <c r="B4" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128331813</v>
       </c>
       <c r="B5" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23955-2025 artfynd.xlsx
+++ b/artfynd/A 23955-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>128331640</v>
       </c>
       <c r="B4" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128331813</v>
       </c>
       <c r="B5" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23955-2025 artfynd.xlsx
+++ b/artfynd/A 23955-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>128331640</v>
       </c>
       <c r="B4" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128331813</v>
       </c>
       <c r="B5" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23955-2025 artfynd.xlsx
+++ b/artfynd/A 23955-2025 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>128331813</v>
       </c>
       <c r="B5" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23955-2025 artfynd.xlsx
+++ b/artfynd/A 23955-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>128331640</v>
       </c>
       <c r="B4" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128331813</v>
       </c>
       <c r="B5" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23955-2025 artfynd.xlsx
+++ b/artfynd/A 23955-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>128331640</v>
       </c>
       <c r="B4" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128331813</v>
       </c>
       <c r="B5" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23955-2025 artfynd.xlsx
+++ b/artfynd/A 23955-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>128331640</v>
       </c>
       <c r="B4" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128331813</v>
       </c>
       <c r="B5" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23955-2025 artfynd.xlsx
+++ b/artfynd/A 23955-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>128331640</v>
       </c>
       <c r="B4" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128331813</v>
       </c>
       <c r="B5" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23955-2025 artfynd.xlsx
+++ b/artfynd/A 23955-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1110,6 +1110,121 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129911849</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98786</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Jangmossen, N om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>407207</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6652345</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>S-Hag-0182</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23955-2025 artfynd.xlsx
+++ b/artfynd/A 23955-2025 artfynd.xlsx
@@ -1115,7 +1115,7 @@
         <v>129911849</v>
       </c>
       <c r="B6" t="n">
-        <v>98786</v>
+        <v>98790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23955-2025 artfynd.xlsx
+++ b/artfynd/A 23955-2025 artfynd.xlsx
@@ -1115,7 +1115,7 @@
         <v>129911849</v>
       </c>
       <c r="B6" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23955-2025 artfynd.xlsx
+++ b/artfynd/A 23955-2025 artfynd.xlsx
@@ -1115,7 +1115,7 @@
         <v>129911849</v>
       </c>
       <c r="B6" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23955-2025 artfynd.xlsx
+++ b/artfynd/A 23955-2025 artfynd.xlsx
@@ -1115,7 +1115,7 @@
         <v>129911849</v>
       </c>
       <c r="B6" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23955-2025 artfynd.xlsx
+++ b/artfynd/A 23955-2025 artfynd.xlsx
@@ -1115,7 +1115,7 @@
         <v>129911849</v>
       </c>
       <c r="B6" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23955-2025 artfynd.xlsx
+++ b/artfynd/A 23955-2025 artfynd.xlsx
@@ -1115,7 +1115,7 @@
         <v>129911849</v>
       </c>
       <c r="B6" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23955-2025 artfynd.xlsx
+++ b/artfynd/A 23955-2025 artfynd.xlsx
@@ -1115,7 +1115,7 @@
         <v>129911849</v>
       </c>
       <c r="B6" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23955-2025 artfynd.xlsx
+++ b/artfynd/A 23955-2025 artfynd.xlsx
@@ -1115,7 +1115,7 @@
         <v>129911849</v>
       </c>
       <c r="B6" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23955-2025 artfynd.xlsx
+++ b/artfynd/A 23955-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123822281</v>
+        <v>128331640</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>407209</v>
+        <v>407245</v>
       </c>
       <c r="R2" t="n">
-        <v>6652333</v>
+        <v>6652297</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,67 +770,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123824769</v>
+        <v>123822281</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Jangmossen, Jangmossen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>407099</v>
+        <v>407209</v>
       </c>
       <c r="R3" t="n">
-        <v>6652218</v>
+        <v>6652333</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,45 +879,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128331640</v>
+        <v>123824769</v>
       </c>
       <c r="B4" t="n">
-        <v>92798</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Jangmossen, Jangmossen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>407245</v>
+        <v>407099</v>
       </c>
       <c r="R4" t="n">
-        <v>6652297</v>
+        <v>6652218</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,22 +949,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:13</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:13</t>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,12 +974,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -999,7 +989,7 @@
         <v>128331813</v>
       </c>
       <c r="B5" t="n">
-        <v>98636</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1105,7 @@
         <v>129911849</v>
       </c>
       <c r="B6" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23955-2025 artfynd.xlsx
+++ b/artfynd/A 23955-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128331640</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123822281</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123824769</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128331813</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1214,8 +1239,20 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129911849</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>